--- a/data/trans_camb/P57_R2-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P57_R2-Edad-trans_camb.xlsx
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,38; 32,69</t>
+          <t>13,75; 32,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,58; 24,08</t>
+          <t>6,29; 24,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,54; 26,75</t>
+          <t>13,89; 27,41</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>31,06; 82,03</t>
+          <t>30,29; 80,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,32; 59,95</t>
+          <t>13,06; 60,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29,52; 64,88</t>
+          <t>30,09; 66,44</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,42; 27,87</t>
+          <t>13,32; 27,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 21,22</t>
+          <t>-7,73; 21,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,1; 21,9</t>
+          <t>3,18; 21,85</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>35,44; 89,91</t>
+          <t>36,27; 90,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-15,93; 62,65</t>
+          <t>-21,54; 62,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,74; 66,13</t>
+          <t>9,67; 65,31</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,91; 24,91</t>
+          <t>12,62; 24,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,3; 25,47</t>
+          <t>15,58; 25,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,95; 23,56</t>
+          <t>15,9; 23,52</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>35,46; 82,25</t>
+          <t>34,62; 80,3</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>46,3; 92,94</t>
+          <t>46,31; 91,81</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>46,89; 78,92</t>
+          <t>46,61; 77,51</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>17,28; 57,58</t>
+          <t>17,51; 56,09</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,35; 20,06</t>
+          <t>8,64; 20,04</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16,0; 45,82</t>
+          <t>15,61; 46,5</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>62,61; 245,83</t>
+          <t>63,71; 227,98</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>38,67; 104,05</t>
+          <t>37,17; 100,66</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>64,25; 201,39</t>
+          <t>61,59; 211,28</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,71; 15,07</t>
+          <t>3,51; 14,65</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,99; 16,22</t>
+          <t>6,8; 16,29</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,83; 14,4</t>
+          <t>6,94; 14,13</t>
         </is>
       </c>
     </row>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>11,73; 64,7</t>
+          <t>12,31; 69,02</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>29,88; 99,24</t>
+          <t>28,62; 96,87</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>27,09; 70,43</t>
+          <t>28,36; 70,09</t>
         </is>
       </c>
     </row>
@@ -1051,17 +1051,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>8,41; 20,55</t>
+          <t>8,19; 21,23</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-8,8; 18,57</t>
+          <t>-9,25; 18,55</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 17,47</t>
+          <t>-6,68; 17,15</t>
         </is>
       </c>
     </row>
@@ -1097,17 +1097,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>28,0; 95,56</t>
+          <t>28,22; 100,32</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-43,82; 119,6</t>
+          <t>-47,4; 119,03</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-26,3; 90,96</t>
+          <t>-29,04; 88,37</t>
         </is>
       </c>
     </row>
@@ -1147,17 +1147,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>7,19; 19,81</t>
+          <t>7,01; 19,67</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>7,21; 17,34</t>
+          <t>7,16; 17,19</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>9,1; 16,88</t>
+          <t>8,77; 16,77</t>
         </is>
       </c>
     </row>
@@ -1193,17 +1193,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>32,18; 129,52</t>
+          <t>29,44; 121,67</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>41,79; 175,81</t>
+          <t>41,11; 170,44</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>51,19; 135,49</t>
+          <t>49,8; 129,07</t>
         </is>
       </c>
     </row>
@@ -1243,17 +1243,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>15,8; 32,13</t>
+          <t>15,76; 31,46</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>4,86; 15,1</t>
+          <t>4,29; 14,96</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>12,05; 22,01</t>
+          <t>12,08; 22,04</t>
         </is>
       </c>
     </row>
@@ -1289,17 +1289,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>51,38; 107,58</t>
+          <t>51,28; 108,38</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>18,02; 58,73</t>
+          <t>17,91; 58,37</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>42,34; 79,69</t>
+          <t>42,32; 78,95</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P57_R2-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P57_R2-Edad-trans_camb.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>23,67</t>
+          <t>22,5</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>15,58</t>
+          <t>14,29</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20,11</t>
+          <t>18,63</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,75; 32,42</t>
+          <t>13,42; 31,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,29; 24,17</t>
+          <t>5,51; 23,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,89; 27,41</t>
+          <t>12,26; 24,7</t>
         </is>
       </c>
     </row>
@@ -594,17 +594,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>51,86%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>42,82%</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>30,29; 80,51</t>
+          <t>28,84; 79,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,06; 60,21</t>
+          <t>11,44; 58,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30,09; 66,44</t>
+          <t>27,44; 60,17</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>20,16</t>
+          <t>20,2</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>11,7</t>
+          <t>18,83</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15,65</t>
+          <t>19,55</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,32; 27,51</t>
+          <t>13,36; 27,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 21,43</t>
+          <t>12,82; 24,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,18; 21,85</t>
+          <t>14,6; 24,03</t>
         </is>
       </c>
     </row>
@@ -690,17 +690,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>60,71%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>53,32%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>57,04%</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>36,27; 90,59</t>
+          <t>37,7; 91,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-21,54; 62,0</t>
+          <t>33,71; 77,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,67; 65,31</t>
+          <t>40,59; 72,76</t>
         </is>
       </c>
     </row>
@@ -740,17 +740,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>18,73</t>
+          <t>16,93</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>20,69</t>
+          <t>19,74</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19,7</t>
+          <t>18,33</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,62; 24,85</t>
+          <t>11,29; 23,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,58; 25,57</t>
+          <t>14,71; 24,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,9; 23,52</t>
+          <t>14,72; 21,79</t>
         </is>
       </c>
     </row>
@@ -786,17 +786,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>55,64%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>64,43%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>56,99%</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>34,62; 80,3</t>
+          <t>30,83; 72,73</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>46,31; 91,81</t>
+          <t>42,64; 87,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>46,61; 77,51</t>
+          <t>43,2; 72,28</t>
         </is>
       </c>
     </row>
@@ -836,17 +836,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>34,25</t>
+          <t>19,01</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>15,1</t>
+          <t>16,24</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26,01</t>
+          <t>17,55</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>17,51; 56,09</t>
+          <t>13,79; 24,71</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,64; 20,04</t>
+          <t>11,67; 20,51</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15,61; 46,5</t>
+          <t>13,85; 20,91</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>128,61%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>72,56%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>106,15%</t>
+          <t>71,65%</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>63,71; 227,98</t>
+          <t>47,7; 106,14</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>37,17; 100,66</t>
+          <t>45,19; 104,39</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>61,59; 211,28</t>
+          <t>52,2; 93,42</t>
         </is>
       </c>
     </row>
@@ -932,17 +932,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>9,26</t>
+          <t>9,42</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>11,65</t>
+          <t>11,7</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10,54</t>
+          <t>10,62</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,51; 14,65</t>
+          <t>4,54; 15,37</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6,8; 16,29</t>
+          <t>6,58; 16,16</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,94; 14,13</t>
+          <t>7,0; 14,28</t>
         </is>
       </c>
     </row>
@@ -978,17 +978,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>58,68%</t>
+          <t>58,91%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>46,47%</t>
         </is>
       </c>
     </row>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>12,31; 69,02</t>
+          <t>14,26; 66,51</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>28,62; 96,87</t>
+          <t>28,65; 96,49</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>28,36; 70,09</t>
+          <t>27,63; 69,54</t>
         </is>
       </c>
     </row>
@@ -1028,17 +1028,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>14,85</t>
+          <t>15,55</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>5,73</t>
+          <t>17,19</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8,41</t>
+          <t>16,51</t>
         </is>
       </c>
     </row>
@@ -1051,17 +1051,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>8,19; 21,23</t>
+          <t>9,28; 21,49</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-9,25; 18,55</t>
+          <t>11,6; 21,46</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 17,15</t>
+          <t>12,58; 20,37</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>104,02%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>81,14%</t>
         </is>
       </c>
     </row>
@@ -1097,17 +1097,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>28,22; 100,32</t>
+          <t>32,52; 104,96</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-47,4; 119,03</t>
+          <t>56,39; 160,92</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-29,04; 88,37</t>
+          <t>53,2; 111,68</t>
         </is>
       </c>
     </row>
@@ -1124,17 +1124,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>13,69</t>
+          <t>14,02</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>12,34</t>
+          <t>12,43</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>12,92</t>
+          <t>13,12</t>
         </is>
       </c>
     </row>
@@ -1147,17 +1147,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>7,01; 19,67</t>
+          <t>7,4; 19,89</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>7,16; 17,19</t>
+          <t>6,76; 17,16</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>8,77; 16,77</t>
+          <t>8,91; 16,89</t>
         </is>
       </c>
     </row>
@@ -1170,17 +1170,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>85,68%</t>
         </is>
       </c>
     </row>
@@ -1193,17 +1193,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>29,44; 121,67</t>
+          <t>32,15; 130,84</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>41,11; 170,44</t>
+          <t>38,38; 168,63</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>49,8; 129,07</t>
+          <t>49,05; 130,27</t>
         </is>
       </c>
     </row>
@@ -1220,17 +1220,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>20,29</t>
+          <t>16,05</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>11,62</t>
+          <t>14,92</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>15,83</t>
+          <t>15,46</t>
         </is>
       </c>
     </row>
@@ -1243,17 +1243,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>15,76; 31,46</t>
+          <t>13,37; 18,51</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>4,29; 14,96</t>
+          <t>12,95; 17,03</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>12,08; 22,04</t>
+          <t>13,87; 17,16</t>
         </is>
       </c>
     </row>
@@ -1266,17 +1266,17 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>52,89%</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>56,66%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>54,63%</t>
         </is>
       </c>
     </row>
@@ -1289,17 +1289,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>51,28; 108,38</t>
+          <t>42,61; 63,83</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>17,91; 58,37</t>
+          <t>46,78; 67,68</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>42,32; 78,95</t>
+          <t>47,31; 62,93</t>
         </is>
       </c>
     </row>
